--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1861952</v>
+        <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hästhuvudmyran, Vb</t>
+          <t>Skottfremyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761079</v>
+        <v>761083</v>
       </c>
       <c r="R2" t="n">
-        <v>7109136</v>
+        <v>7109046</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Sävar</t>
+          <t>Umeå socken</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,29 +772,135 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Felix Gustafsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Felix Gustafsson, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137305925</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1861952</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästhuvudmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>761079</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7109136</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1861952</t>
         </is>
@@ -797,6 +909,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,6 +903,123 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/1861952</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137325090</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inventering 17 oktober, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>761131</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7108982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137325090</t>
         </is>
       </c>
     </row>
@@ -910,6 +1027,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,52 +792,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1861952</v>
+        <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästhuvudmyran, Vb</t>
+          <t>Skottfremyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761079</v>
+        <v>761112</v>
       </c>
       <c r="R3" t="n">
-        <v>7109136</v>
+        <v>7108962</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +852,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Sävar</t>
+          <t>Umeå socken</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,84 +883,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1861952</t>
+          <t>https://artportalen.se/Sighting/137337637</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137325090</v>
+        <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>99405</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Inventering 17 oktober, Vb</t>
+          <t>Skottfremyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761131</v>
+        <v>761109</v>
       </c>
       <c r="R4" t="n">
-        <v>7108982</v>
+        <v>7109008</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +964,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sävar</t>
+          <t>Umeå socken</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,16 +999,606 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Clara Alskog</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Clara Alskog</t>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137337668</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137337641</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92591</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skottfremyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>761103</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7109054</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137337641</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137337640</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96620</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skottfremyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>761118</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7109016</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137337640</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1861952</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästhuvudmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>761079</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7109136</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-12-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Hällström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1861952</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137337639</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skottfremyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>761121</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7109020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>stubbe, grantickeangripen</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # stubbe, grantickeangripen</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137337639</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137325090</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inventering 17 oktober, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>761131</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7108982</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137325090</t>
         </is>
@@ -1028,6 +1609,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137337641</v>
       </c>
       <c r="B5" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337640</v>
       </c>
       <c r="B6" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137337639</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>137325090</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137337641</v>
+        <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92594</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skottfremyran, Vb</t>
+          <t>Bodbyn, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761103</v>
+        <v>761110</v>
       </c>
       <c r="R5" t="n">
-        <v>7109054</v>
+        <v>7108987</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sävar</t>
+          <t>Umeå socken</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1111,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137337641</t>
+          <t>https://artportalen.se/Sighting/137376384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137337640</v>
+        <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>96625</v>
+        <v>92596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761118</v>
+        <v>761103</v>
       </c>
       <c r="R6" t="n">
-        <v>7109016</v>
+        <v>7109054</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,58 +1234,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137337640</t>
+          <t>https://artportalen.se/Sighting/137337641</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1861952</v>
+        <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>96627</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästhuvudmyran, Vb</t>
+          <t>Skottfremyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>761079</v>
+        <v>761118</v>
       </c>
       <c r="R7" t="n">
-        <v>7109136</v>
+        <v>7109016</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,12 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-12-28</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,80 +1331,73 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Hällström</t>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1861952</t>
+          <t>https://artportalen.se/Sighting/137337640</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137337639</v>
+        <v>1861952</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skottfremyran, Vb</t>
+          <t>Hästhuvudmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761121</v>
+        <v>761079</v>
       </c>
       <c r="R8" t="n">
-        <v>7109020</v>
+        <v>7109136</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,22 +1421,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2011-12-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2011-12-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,93 +1438,79 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>stubbe, grantickeangripen</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # stubbe, grantickeangripen</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
+          <t>Anders Hällström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137337639</t>
+          <t>https://artportalen.se/Sighting/1861952</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137325090</v>
+        <v>137337639</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Inventering 17 oktober, Vb</t>
+          <t>Skottfremyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761131</v>
+        <v>761121</v>
       </c>
       <c r="R9" t="n">
-        <v>7108982</v>
+        <v>7109020</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,20 +1560,157 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>stubbe, grantickeangripen</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # stubbe, grantickeangripen</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Clara Alskog</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Clara Alskog</t>
+          <t>Alva Danielsson, Felix Gustafsson, Alice Thomander, Carl Jansson, Jonas Eilertsen, Jorma Salmgren, Clara Alskog, Felicia Oskarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137337639</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137325090</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inventering 17 oktober, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>761131</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7108982</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Clara Alskog</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137325090</t>
         </is>
@@ -1614,6 +1726,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137337639</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>137325090</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>137325090</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>137325090</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>137325090</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 10945-2025 artfynd.xlsx
+++ b/artfynd/A 10945-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137305925</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137337637</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137337668</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137376384</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137337641</v>
       </c>
       <c r="B6" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137337640</v>
       </c>
       <c r="B7" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137337639</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>137325090</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
